--- a/docentes/Rivera Cruz Ezequiel - Estadisticos 20231.xlsx
+++ b/docentes/Rivera Cruz Ezequiel - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="61">
   <si>
     <t>Mat</t>
   </si>
@@ -76,61 +76,127 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>AYOHUA</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>JENKINS</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
     <t>HERRERA</t>
   </si>
   <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>MELCHOR</t>
+  </si>
+  <si>
     <t>PEREZ</t>
   </si>
   <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>MELCHOR</t>
-  </si>
-  <si>
     <t>ROBLES</t>
   </si>
   <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
     <t>ZEPAHUA</t>
   </si>
   <si>
+    <t>COXCAHUA</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>COYOHUA</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>QUERO</t>
+  </si>
+  <si>
     <t>AVELINO</t>
   </si>
   <si>
     <t>ACOSTA</t>
   </si>
   <si>
+    <t>ZEPEDA</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
     <t>ROMERO</t>
   </si>
   <si>
-    <t>ZEPEDA</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
     <t>LOPEZ</t>
   </si>
   <si>
+    <t>SALOMON</t>
+  </si>
+  <si>
     <t>TEXCAHUA</t>
   </si>
   <si>
+    <t>FRANCISCO JAVIER</t>
+  </si>
+  <si>
+    <t>CARLOS YAEL</t>
+  </si>
+  <si>
+    <t>ARTHUR RICHARD</t>
+  </si>
+  <si>
+    <t>EDER</t>
+  </si>
+  <si>
+    <t>DIEGO</t>
+  </si>
+  <si>
+    <t>CRISTHIAN</t>
+  </si>
+  <si>
+    <t>DIEGO JESUS</t>
+  </si>
+  <si>
     <t>KEVIN</t>
   </si>
   <si>
     <t>MIGUEL ANTONIO</t>
   </si>
   <si>
+    <t>ROGGER JUSEFH</t>
+  </si>
+  <si>
+    <t>ALDAHIR</t>
+  </si>
+  <si>
     <t>JULIAN DAVID</t>
   </si>
   <si>
-    <t>ROGGER JUSEFH</t>
-  </si>
-  <si>
-    <t>ALDAHIR</t>
-  </si>
-  <si>
     <t>ABIEL NEFTALI</t>
+  </si>
+  <si>
+    <t>DANIEL</t>
   </si>
   <si>
     <t>GEOVANNI</t>
@@ -908,7 +974,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -940,22 +1006,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920018</v>
+        <v>22330051920333</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D2" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -963,16 +1029,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920038</v>
+        <v>22330051920034</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D3" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -986,16 +1052,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920045</v>
+        <v>22330051920189</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D4" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1009,22 +1075,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920039</v>
+        <v>22330051920006</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -1032,22 +1098,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920191</v>
+        <v>22330051920010</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D6" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -1055,22 +1121,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920047</v>
+        <v>22330051920013</v>
       </c>
       <c r="B7" t="s">
         <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="D7" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -1078,24 +1144,208 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920051</v>
+        <v>22330051920015</v>
       </c>
       <c r="B8" t="s">
         <v>24</v>
       </c>
       <c r="C8" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" t="s">
+        <v>52</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>22330051920018</v>
+      </c>
+      <c r="B9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D9" t="s">
+        <v>53</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>9</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>22330051920038</v>
+      </c>
+      <c r="B10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" t="s">
+        <v>54</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>22330051920039</v>
+      </c>
+      <c r="B11" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D11" t="s">
+        <v>55</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>22330051920191</v>
+      </c>
+      <c r="B12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12" t="s">
+        <v>56</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>22330051920045</v>
+      </c>
+      <c r="B13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" t="s">
+        <v>42</v>
+      </c>
+      <c r="D13" t="s">
+        <v>57</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>22330051920047</v>
+      </c>
+      <c r="B14" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" t="s">
+        <v>43</v>
+      </c>
+      <c r="D14" t="s">
+        <v>58</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>22330051920049</v>
+      </c>
+      <c r="B15" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" t="s">
+        <v>44</v>
+      </c>
+      <c r="D15" t="s">
+        <v>59</v>
+      </c>
+      <c r="E15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>22330051920051</v>
+      </c>
+      <c r="B16" t="s">
         <v>31</v>
       </c>
-      <c r="D8" t="s">
-        <v>38</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
+      <c r="C16" t="s">
+        <v>45</v>
+      </c>
+      <c r="D16" t="s">
+        <v>60</v>
+      </c>
+      <c r="E16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" t="s">
         <v>12</v>
       </c>
-      <c r="G8">
+      <c r="G16">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Rivera Cruz Ezequiel - Estadisticos 20231.xlsx
+++ b/docentes/Rivera Cruz Ezequiel - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="58">
   <si>
     <t>Mat</t>
   </si>
@@ -76,9 +76,6 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>AYOHUA</t>
-  </si>
-  <si>
     <t>CRUZ</t>
   </si>
   <si>
@@ -115,9 +112,6 @@
     <t>ZEPAHUA</t>
   </si>
   <si>
-    <t>COXCAHUA</t>
-  </si>
-  <si>
     <t>REYES</t>
   </si>
   <si>
@@ -155,9 +149,6 @@
   </si>
   <si>
     <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>FRANCISCO JAVIER</t>
   </si>
   <si>
     <t>CARLOS YAEL</t>
@@ -789,16 +780,19 @@
         <v>42</v>
       </c>
       <c r="D4">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>97.62</v>
+      </c>
+      <c r="H4">
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -929,16 +923,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G4">
-        <v>92.86</v>
+        <v>97.62</v>
       </c>
       <c r="H4">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -974,7 +968,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1006,22 +1000,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920333</v>
+        <v>22330051920034</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1029,16 +1023,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920034</v>
+        <v>22330051920189</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1052,39 +1046,39 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920189</v>
+        <v>22330051920006</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="D4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920006</v>
+        <v>22330051920010</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1098,16 +1092,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920010</v>
+        <v>22330051920013</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1121,16 +1115,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920013</v>
+        <v>22330051920015</v>
       </c>
       <c r="B7" t="s">
         <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1144,16 +1138,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920015</v>
+        <v>22330051920018</v>
       </c>
       <c r="B8" t="s">
         <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D8" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1167,22 +1161,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920018</v>
+        <v>22330051920038</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D9" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -1190,16 +1184,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920038</v>
+        <v>22330051920039</v>
       </c>
       <c r="B10" t="s">
         <v>25</v>
       </c>
       <c r="C10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D10" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1213,16 +1207,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920039</v>
+        <v>22330051920191</v>
       </c>
       <c r="B11" t="s">
         <v>26</v>
       </c>
       <c r="C11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D11" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1236,16 +1230,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920191</v>
+        <v>22330051920045</v>
       </c>
       <c r="B12" t="s">
         <v>27</v>
       </c>
       <c r="C12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D12" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1259,16 +1253,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920045</v>
+        <v>22330051920047</v>
       </c>
       <c r="B13" t="s">
         <v>28</v>
       </c>
       <c r="C13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D13" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1282,16 +1276,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920047</v>
+        <v>22330051920049</v>
       </c>
       <c r="B14" t="s">
         <v>29</v>
       </c>
       <c r="C14" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D14" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1305,16 +1299,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920049</v>
+        <v>22330051920051</v>
       </c>
       <c r="B15" t="s">
         <v>30</v>
       </c>
       <c r="C15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D15" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1323,29 +1317,6 @@
         <v>12</v>
       </c>
       <c r="G15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>22330051920051</v>
-      </c>
-      <c r="B16" t="s">
-        <v>31</v>
-      </c>
-      <c r="C16" t="s">
-        <v>45</v>
-      </c>
-      <c r="D16" t="s">
-        <v>60</v>
-      </c>
-      <c r="E16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" t="s">
-        <v>12</v>
-      </c>
-      <c r="G16">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Rivera Cruz Ezequiel - Estadisticos 20231.xlsx
+++ b/docentes/Rivera Cruz Ezequiel - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="53">
   <si>
     <t>Mat</t>
   </si>
@@ -91,7 +91,7 @@
     <t>GARCIA</t>
   </si>
   <si>
-    <t>HERRERA</t>
+    <t>GUERRA</t>
   </si>
   <si>
     <t>LUNA</t>
@@ -109,9 +109,6 @@
     <t>VENTURA</t>
   </si>
   <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
     <t>REYES</t>
   </si>
   <si>
@@ -127,10 +124,7 @@
     <t>QUERO</t>
   </si>
   <si>
-    <t>AVELINO</t>
-  </si>
-  <si>
-    <t>ACOSTA</t>
+    <t>JERONIMO</t>
   </si>
   <si>
     <t>ZEPEDA</t>
@@ -148,9 +142,6 @@
     <t>SALOMON</t>
   </si>
   <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
     <t>CARLOS YAEL</t>
   </si>
   <si>
@@ -169,10 +160,7 @@
     <t>DIEGO JESUS</t>
   </si>
   <si>
-    <t>KEVIN</t>
-  </si>
-  <si>
-    <t>MIGUEL ANTONIO</t>
+    <t>LUIS</t>
   </si>
   <si>
     <t>ROGGER JUSEFH</t>
@@ -188,9 +176,6 @@
   </si>
   <si>
     <t>DANIEL</t>
-  </si>
-  <si>
-    <t>GEOVANNI</t>
   </si>
 </sst>
 </file>
@@ -734,16 +719,19 @@
         <v>30</v>
       </c>
       <c r="D2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>80</v>
+      </c>
+      <c r="H2">
+        <v>7.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -757,16 +745,19 @@
         <v>42</v>
       </c>
       <c r="D3">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>97.62</v>
+      </c>
+      <c r="H3">
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -806,16 +797,19 @@
         <v>32</v>
       </c>
       <c r="D5">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>75</v>
+      </c>
+      <c r="H5">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -880,7 +874,7 @@
         <v>80</v>
       </c>
       <c r="H2">
-        <v>7.8</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -906,7 +900,7 @@
         <v>97.62</v>
       </c>
       <c r="H3">
-        <v>9</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -949,16 +943,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F5">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G5">
-        <v>68.75</v>
+        <v>75</v>
       </c>
       <c r="H5">
-        <v>7</v>
+        <v>7.5</v>
       </c>
     </row>
   </sheetData>
@@ -968,7 +962,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1006,10 +1000,10 @@
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1032,7 +1026,7 @@
         <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1052,10 +1046,10 @@
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1075,10 +1069,10 @@
         <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1098,10 +1092,10 @@
         <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D6" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1121,10 +1115,10 @@
         <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1138,16 +1132,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920018</v>
+        <v>22330051920017</v>
       </c>
       <c r="B8" t="s">
         <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D8" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1161,16 +1155,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920038</v>
+        <v>22330051920039</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D9" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1184,16 +1178,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920039</v>
+        <v>22330051920191</v>
       </c>
       <c r="B10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D10" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1207,16 +1201,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920191</v>
+        <v>22330051920045</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D11" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1230,16 +1224,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920045</v>
+        <v>22330051920047</v>
       </c>
       <c r="B12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D12" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1253,16 +1247,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920047</v>
+        <v>22330051920049</v>
       </c>
       <c r="B13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D13" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1271,52 +1265,6 @@
         <v>12</v>
       </c>
       <c r="G13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>22330051920049</v>
-      </c>
-      <c r="B14" t="s">
-        <v>29</v>
-      </c>
-      <c r="C14" t="s">
-        <v>42</v>
-      </c>
-      <c r="D14" t="s">
-        <v>56</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>12</v>
-      </c>
-      <c r="G14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>22330051920051</v>
-      </c>
-      <c r="B15" t="s">
-        <v>30</v>
-      </c>
-      <c r="C15" t="s">
-        <v>43</v>
-      </c>
-      <c r="D15" t="s">
-        <v>57</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>12</v>
-      </c>
-      <c r="G15">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Rivera Cruz Ezequiel - Estadisticos 20231.xlsx
+++ b/docentes/Rivera Cruz Ezequiel - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="47">
   <si>
     <t>Mat</t>
   </si>
@@ -97,18 +97,12 @@
     <t>LUNA</t>
   </si>
   <si>
-    <t>MELCHOR</t>
-  </si>
-  <si>
     <t>PEREZ</t>
   </si>
   <si>
     <t>ROBLES</t>
   </si>
   <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
     <t>REYES</t>
   </si>
   <si>
@@ -130,18 +124,12 @@
     <t>ZEPEDA</t>
   </si>
   <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
     <t>ROMERO</t>
   </si>
   <si>
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>SALOMON</t>
-  </si>
-  <si>
     <t>CARLOS YAEL</t>
   </si>
   <si>
@@ -166,16 +154,10 @@
     <t>ROGGER JUSEFH</t>
   </si>
   <si>
-    <t>ALDAHIR</t>
-  </si>
-  <si>
     <t>JULIAN DAVID</t>
   </si>
   <si>
     <t>ABIEL NEFTALI</t>
-  </si>
-  <si>
-    <t>DANIEL</t>
   </si>
 </sst>
 </file>
@@ -800,13 +782,13 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F5">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G5">
-        <v>75</v>
+        <v>81.25</v>
       </c>
       <c r="H5">
         <v>7</v>
@@ -874,7 +856,7 @@
         <v>80</v>
       </c>
       <c r="H2">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -943,16 +925,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F5">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G5">
-        <v>75</v>
+        <v>81.25</v>
       </c>
       <c r="H5">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
     </row>
   </sheetData>
@@ -962,7 +944,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1000,10 +982,10 @@
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1026,7 +1008,7 @@
         <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1046,10 +1028,10 @@
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D4" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1069,10 +1051,10 @@
         <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1092,10 +1074,10 @@
         <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D6" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1115,10 +1097,10 @@
         <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D7" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1138,10 +1120,10 @@
         <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D8" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1161,10 +1143,10 @@
         <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D9" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1178,16 +1160,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920191</v>
+        <v>22330051920045</v>
       </c>
       <c r="B10" t="s">
         <v>26</v>
       </c>
       <c r="C10" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D10" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1201,16 +1183,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920045</v>
+        <v>22330051920047</v>
       </c>
       <c r="B11" t="s">
         <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D11" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1219,52 +1201,6 @@
         <v>12</v>
       </c>
       <c r="G11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>22330051920047</v>
-      </c>
-      <c r="B12" t="s">
-        <v>28</v>
-      </c>
-      <c r="C12" t="s">
-        <v>39</v>
-      </c>
-      <c r="D12" t="s">
-        <v>51</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>12</v>
-      </c>
-      <c r="G12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>22330051920049</v>
-      </c>
-      <c r="B13" t="s">
-        <v>29</v>
-      </c>
-      <c r="C13" t="s">
-        <v>40</v>
-      </c>
-      <c r="D13" t="s">
-        <v>52</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>12</v>
-      </c>
-      <c r="G13">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Rivera Cruz Ezequiel - Estadisticos 20231.xlsx
+++ b/docentes/Rivera Cruz Ezequiel - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="32">
   <si>
     <t>Mat</t>
   </si>
@@ -76,58 +76,34 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>REYES</t>
+  </si>
+  <si>
     <t>CRUZ</t>
   </si>
   <si>
     <t>JENKINS</t>
   </si>
   <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>FLORES</t>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>JOAQUIN</t>
+  </si>
+  <si>
+    <t>COYOHUA</t>
   </si>
   <si>
     <t>GARCIA</t>
   </si>
   <si>
-    <t>GUERRA</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>COYOHUA</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>QUERO</t>
-  </si>
-  <si>
-    <t>JERONIMO</t>
-  </si>
-  <si>
     <t>ZEPEDA</t>
   </si>
   <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
+    <t>DANIEL</t>
+  </si>
+  <si>
+    <t>DIEGO</t>
   </si>
   <si>
     <t>CARLOS YAEL</t>
@@ -136,28 +112,7 @@
     <t>ARTHUR RICHARD</t>
   </si>
   <si>
-    <t>EDER</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
-  </si>
-  <si>
-    <t>CRISTHIAN</t>
-  </si>
-  <si>
-    <t>DIEGO JESUS</t>
-  </si>
-  <si>
-    <t>LUIS</t>
-  </si>
-  <si>
     <t>ROGGER JUSEFH</t>
-  </si>
-  <si>
-    <t>JULIAN DAVID</t>
-  </si>
-  <si>
-    <t>ABIEL NEFTALI</t>
   </si>
 </sst>
 </file>
@@ -847,16 +802,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G2">
-        <v>80</v>
+        <v>93.33</v>
       </c>
       <c r="H2">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -873,16 +828,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G3">
-        <v>97.62</v>
+        <v>100</v>
       </c>
       <c r="H3">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -899,16 +854,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G4">
-        <v>97.62</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="H4">
-        <v>9</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -925,16 +880,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G5">
-        <v>81.25</v>
+        <v>87.5</v>
       </c>
       <c r="H5">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
     </row>
   </sheetData>
@@ -944,7 +899,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -976,22 +931,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920034</v>
+        <v>20330051920059</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -999,45 +954,45 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920189</v>
+        <v>22330051920010</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920006</v>
+        <v>22330051920034</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" t="s">
         <v>29</v>
       </c>
-      <c r="D4" t="s">
-        <v>39</v>
-      </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -1045,22 +1000,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920010</v>
+        <v>22330051920189</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" t="s">
         <v>30</v>
       </c>
-      <c r="D5" t="s">
-        <v>40</v>
-      </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -1068,139 +1023,24 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920013</v>
+        <v>22330051920039</v>
       </c>
       <c r="B6" t="s">
         <v>22</v>
       </c>
       <c r="C6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" t="s">
         <v>31</v>
       </c>
-      <c r="D6" t="s">
-        <v>41</v>
-      </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>22330051920015</v>
-      </c>
-      <c r="B7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D7" t="s">
-        <v>42</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>9</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>22330051920017</v>
-      </c>
-      <c r="B8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" t="s">
-        <v>33</v>
-      </c>
-      <c r="D8" t="s">
-        <v>43</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>22330051920039</v>
-      </c>
-      <c r="B9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" t="s">
-        <v>34</v>
-      </c>
-      <c r="D9" t="s">
-        <v>44</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>12</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>22330051920045</v>
-      </c>
-      <c r="B10" t="s">
-        <v>26</v>
-      </c>
-      <c r="C10" t="s">
-        <v>35</v>
-      </c>
-      <c r="D10" t="s">
-        <v>45</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>12</v>
-      </c>
-      <c r="G10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>22330051920047</v>
-      </c>
-      <c r="B11" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11" t="s">
-        <v>36</v>
-      </c>
-      <c r="D11" t="s">
-        <v>46</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G11">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Rivera Cruz Ezequiel - Estadisticos 20231.xlsx
+++ b/docentes/Rivera Cruz Ezequiel - Estadisticos 20231.xlsx
@@ -811,7 +811,7 @@
         <v>93.33</v>
       </c>
       <c r="H2">
-        <v>8.300000000000001</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -837,7 +837,7 @@
         <v>100</v>
       </c>
       <c r="H3">
-        <v>9.300000000000001</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -863,7 +863,7 @@
         <v>95.23999999999999</v>
       </c>
       <c r="H4">
-        <v>8.9</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -889,7 +889,7 @@
         <v>87.5</v>
       </c>
       <c r="H5">
-        <v>7.7</v>
+        <v>9.4</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Rivera Cruz Ezequiel - Estadisticos 20231.xlsx
+++ b/docentes/Rivera Cruz Ezequiel - Estadisticos 20231.xlsx
@@ -811,7 +811,7 @@
         <v>93.33</v>
       </c>
       <c r="H2">
-        <v>9.699999999999999</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -837,7 +837,7 @@
         <v>100</v>
       </c>
       <c r="H3">
-        <v>10</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -863,7 +863,7 @@
         <v>95.23999999999999</v>
       </c>
       <c r="H4">
-        <v>9.800000000000001</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -889,7 +889,7 @@
         <v>87.5</v>
       </c>
       <c r="H5">
-        <v>9.4</v>
+        <v>7.7</v>
       </c>
     </row>
   </sheetData>
